--- a/academias/La Materia y sus Interacciones - Estadisticos 20232.xlsx
+++ b/academias/La Materia y sus Interacciones - Estadisticos 20232.xlsx
@@ -796,25 +796,25 @@
         <v>31</v>
       </c>
       <c r="E10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F10">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G10" s="1">
-        <v>54.8</v>
+        <v>58.1</v>
       </c>
       <c r="H10" s="1">
-        <v>45.2</v>
+        <v>41.9</v>
       </c>
       <c r="I10" s="2">
         <v>6.5</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>3.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -901,25 +901,25 @@
         <v>38</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F13">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>89.5</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>10.5</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J13">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -933,25 +933,25 @@
         <v>192</v>
       </c>
       <c r="E14">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="F14">
-        <v>103</v>
+        <v>68</v>
       </c>
       <c r="G14" s="1">
-        <v>46.4</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>53.6</v>
+        <v>35.4</v>
       </c>
       <c r="I14" s="2">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="J14">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>20.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -962,25 +962,25 @@
         <v>319</v>
       </c>
       <c r="E15">
-        <v>178</v>
+        <v>213</v>
       </c>
       <c r="F15">
-        <v>141</v>
+        <v>106</v>
       </c>
       <c r="G15" s="1">
-        <v>55.8</v>
+        <v>66.8</v>
       </c>
       <c r="H15" s="1">
-        <v>44.2</v>
+        <v>33.2</v>
       </c>
       <c r="I15" s="2">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="J15">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>12.2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1048,25 +1048,25 @@
         <v>30</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>56.7</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>43.3</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1083,25 +1083,25 @@
         <v>29</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>82.8</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>17.2</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J3">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1118,25 +1118,25 @@
         <v>23</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>17.4</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J4">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1153,25 +1153,25 @@
         <v>33</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F5">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>57.6</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>42.4</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J5">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1188,25 +1188,25 @@
         <v>12</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1220,25 +1220,25 @@
         <v>127</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="F7">
-        <v>127</v>
+        <v>40</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>68.5</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>31.5</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J7">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1255,25 +1255,25 @@
         <v>25</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F8">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J8">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1290,25 +1290,25 @@
         <v>39</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F9">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>71.8</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>28.2</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J9">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1325,25 +1325,25 @@
         <v>31</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F10">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>74.2</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>25.8</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J10">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1360,25 +1360,25 @@
         <v>35</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F11">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>31.4</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J11">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1395,25 +1395,25 @@
         <v>24</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F12">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>58.3</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>41.7</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J12">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1430,25 +1430,25 @@
         <v>38</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F13">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>89.5</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>10.5</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J13">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1462,25 +1462,25 @@
         <v>192</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="F14">
-        <v>192</v>
+        <v>55</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>28.6</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J14">
-        <v>192</v>
+        <v>1</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1491,25 +1491,25 @@
         <v>319</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="F15">
-        <v>319</v>
+        <v>95</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>70.2</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>29.8</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J15">
-        <v>319</v>
+        <v>1</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -1577,16 +1577,16 @@
         <v>30</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" s="1">
-        <v>60</v>
+        <v>56.7</v>
       </c>
       <c r="H2" s="1">
-        <v>40</v>
+        <v>43.3</v>
       </c>
       <c r="I2" s="2">
         <v>6.6</v>
@@ -1659,7 +1659,7 @@
         <v>17.4</v>
       </c>
       <c r="I4" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1694,7 +1694,7 @@
         <v>42.4</v>
       </c>
       <c r="I5" s="2">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1717,19 +1717,19 @@
         <v>12</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="H6" s="1">
-        <v>25</v>
+        <v>33.3</v>
       </c>
       <c r="I6" s="2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1749,19 +1749,19 @@
         <v>127</v>
       </c>
       <c r="E7">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G7" s="1">
-        <v>70.09999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="H7" s="1">
-        <v>29.9</v>
+        <v>31.5</v>
       </c>
       <c r="I7" s="2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1796,7 +1796,7 @@
         <v>44</v>
       </c>
       <c r="I8" s="2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1819,19 +1819,19 @@
         <v>39</v>
       </c>
       <c r="E9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9" s="1">
-        <v>69.2</v>
+        <v>71.8</v>
       </c>
       <c r="H9" s="1">
-        <v>30.8</v>
+        <v>28.2</v>
       </c>
       <c r="I9" s="2">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1854,25 +1854,25 @@
         <v>31</v>
       </c>
       <c r="E10">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F10">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G10" s="1">
-        <v>54.8</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>45.2</v>
+        <v>22.6</v>
       </c>
       <c r="I10" s="2">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>3.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1889,19 +1889,19 @@
         <v>35</v>
       </c>
       <c r="E11">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F11">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G11" s="1">
-        <v>57.1</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>42.9</v>
+        <v>31.4</v>
       </c>
       <c r="I11" s="2">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1924,19 +1924,19 @@
         <v>24</v>
       </c>
       <c r="E12">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F12">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G12" s="1">
-        <v>45.8</v>
+        <v>58.3</v>
       </c>
       <c r="H12" s="1">
-        <v>54.2</v>
+        <v>41.7</v>
       </c>
       <c r="I12" s="2">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1959,25 +1959,25 @@
         <v>38</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F13">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>89.5</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>10.5</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J13">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1991,25 +1991,25 @@
         <v>192</v>
       </c>
       <c r="E14">
-        <v>89</v>
+        <v>138</v>
       </c>
       <c r="F14">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="G14" s="1">
-        <v>46.4</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>53.6</v>
+        <v>28.1</v>
       </c>
       <c r="I14" s="2">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="J14">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>20.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2020,25 +2020,25 @@
         <v>319</v>
       </c>
       <c r="E15">
-        <v>178</v>
+        <v>225</v>
       </c>
       <c r="F15">
-        <v>141</v>
+        <v>94</v>
       </c>
       <c r="G15" s="1">
-        <v>55.8</v>
+        <v>70.5</v>
       </c>
       <c r="H15" s="1">
-        <v>44.2</v>
+        <v>29.5</v>
       </c>
       <c r="I15" s="2">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="J15">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>12.2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/La Materia y sus Interacciones - Estadisticos 20232.xlsx
+++ b/academias/La Materia y sus Interacciones - Estadisticos 20232.xlsx
@@ -1325,25 +1325,25 @@
         <v>31</v>
       </c>
       <c r="E10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G10" s="1">
-        <v>74.2</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>25.8</v>
+        <v>22.6</v>
       </c>
       <c r="I10" s="2">
         <v>7.5</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>3.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1462,25 +1462,25 @@
         <v>192</v>
       </c>
       <c r="E14">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F14">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G14" s="1">
-        <v>71.40000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>28.6</v>
+        <v>28.1</v>
       </c>
       <c r="I14" s="2">
         <v>7.1</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1491,25 +1491,25 @@
         <v>319</v>
       </c>
       <c r="E15">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F15">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G15" s="1">
-        <v>70.2</v>
+        <v>70.5</v>
       </c>
       <c r="H15" s="1">
-        <v>29.8</v>
+        <v>29.5</v>
       </c>
       <c r="I15" s="2">
         <v>7</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1577,19 +1577,19 @@
         <v>30</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G2" s="1">
-        <v>56.7</v>
+        <v>80</v>
       </c>
       <c r="H2" s="1">
-        <v>43.3</v>
+        <v>20</v>
       </c>
       <c r="I2" s="2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1612,19 +1612,19 @@
         <v>29</v>
       </c>
       <c r="E3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>82.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>17.2</v>
+        <v>3.4</v>
       </c>
       <c r="I3" s="2">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1647,16 +1647,16 @@
         <v>23</v>
       </c>
       <c r="E4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>82.59999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="H4" s="1">
-        <v>17.4</v>
+        <v>4.3</v>
       </c>
       <c r="I4" s="2">
         <v>7.7</v>
@@ -1682,19 +1682,19 @@
         <v>33</v>
       </c>
       <c r="E5">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F5">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>57.6</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>42.4</v>
+        <v>6.1</v>
       </c>
       <c r="I5" s="2">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1717,19 +1717,19 @@
         <v>12</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="H6" s="1">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="I6" s="2">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1749,19 +1749,19 @@
         <v>127</v>
       </c>
       <c r="E7">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="F7">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="G7" s="1">
-        <v>68.5</v>
+        <v>89.8</v>
       </c>
       <c r="H7" s="1">
-        <v>31.5</v>
+        <v>10.2</v>
       </c>
       <c r="I7" s="2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1784,19 +1784,19 @@
         <v>25</v>
       </c>
       <c r="E8">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G8" s="1">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="H8" s="1">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="I8" s="2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1819,19 +1819,19 @@
         <v>39</v>
       </c>
       <c r="E9">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F9">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>71.8</v>
+        <v>89.7</v>
       </c>
       <c r="H9" s="1">
-        <v>28.2</v>
+        <v>10.3</v>
       </c>
       <c r="I9" s="2">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1854,19 +1854,19 @@
         <v>31</v>
       </c>
       <c r="E10">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F10">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G10" s="1">
-        <v>77.40000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="H10" s="1">
-        <v>22.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I10" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1889,19 +1889,19 @@
         <v>35</v>
       </c>
       <c r="E11">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F11">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>68.59999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>31.4</v>
+        <v>17.1</v>
       </c>
       <c r="I11" s="2">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1924,19 +1924,19 @@
         <v>24</v>
       </c>
       <c r="E12">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F12">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>58.3</v>
+        <v>95.8</v>
       </c>
       <c r="H12" s="1">
-        <v>41.7</v>
+        <v>4.2</v>
       </c>
       <c r="I12" s="2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1959,19 +1959,19 @@
         <v>38</v>
       </c>
       <c r="E13">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G13" s="1">
-        <v>89.5</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>10.5</v>
+        <v>2.6</v>
       </c>
       <c r="I13" s="2">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1991,19 +1991,19 @@
         <v>192</v>
       </c>
       <c r="E14">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="F14">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="G14" s="1">
-        <v>71.90000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="H14" s="1">
-        <v>28.1</v>
+        <v>11.5</v>
       </c>
       <c r="I14" s="2">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2020,19 +2020,19 @@
         <v>319</v>
       </c>
       <c r="E15">
-        <v>225</v>
+        <v>284</v>
       </c>
       <c r="F15">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="G15" s="1">
-        <v>70.5</v>
+        <v>89</v>
       </c>
       <c r="H15" s="1">
-        <v>29.5</v>
+        <v>11</v>
       </c>
       <c r="I15" s="2">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="J15">
         <v>0</v>
